--- a/Thesis Forecasting/PAPER CONTEXT/tables/appendix_F_daily_total_generation_summary.xlsx
+++ b/Thesis Forecasting/PAPER CONTEXT/tables/appendix_F_daily_total_generation_summary.xlsx
@@ -459,16 +459,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1443.987696048894</v>
+        <v>1440.970224806281</v>
       </c>
       <c r="C2" t="n">
-        <v>60.16615400203727</v>
+        <v>60.04042603359503</v>
       </c>
       <c r="D2" t="n">
-        <v>60.17080000016298</v>
+        <v>60.77480860576034</v>
       </c>
       <c r="E2" t="n">
-        <v>60.16150800391155</v>
+        <v>58.9534736140165</v>
       </c>
     </row>
     <row r="3">
@@ -478,16 +478,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3118.198799944116</v>
+        <v>3101.053318055117</v>
       </c>
       <c r="C3" t="n">
-        <v>129.9249499976715</v>
+        <v>129.2105549189632</v>
       </c>
       <c r="D3" t="n">
-        <v>129.9678679998137</v>
+        <v>129.9116017993481</v>
       </c>
       <c r="E3" t="n">
-        <v>129.8820319955293</v>
+        <v>128.4157296687362</v>
       </c>
     </row>
     <row r="4">
@@ -497,16 +497,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3376.330799998252</v>
+        <v>3375.113497993018</v>
       </c>
       <c r="C4" t="n">
-        <v>140.6804499999272</v>
+        <v>140.6297290830424</v>
       </c>
       <c r="D4" t="n">
-        <v>140.6999999998602</v>
+        <v>140.6914999998603</v>
       </c>
       <c r="E4" t="n">
-        <v>140.6608999999942</v>
+        <v>140.5483999996044</v>
       </c>
     </row>
     <row r="5">
@@ -516,16 +516,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1019.407492825218</v>
+        <v>1004.981327375173</v>
       </c>
       <c r="C5" t="n">
-        <v>42.47531220105077</v>
+        <v>41.87422197396554</v>
       </c>
       <c r="D5" t="n">
-        <v>48.07514461446019</v>
+        <v>42.71673199988358</v>
       </c>
       <c r="E5" t="n">
-        <v>38.09874270093729</v>
+        <v>41.41243241979362</v>
       </c>
     </row>
     <row r="6">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3778.80419998604</v>
+        <v>3771.410049993013</v>
       </c>
       <c r="C6" t="n">
-        <v>157.4501749994183</v>
+        <v>157.1420854163755</v>
       </c>
       <c r="D6" t="n">
-        <v>157.5266499999535</v>
+        <v>157.6315999999534</v>
       </c>
       <c r="E6" t="n">
-        <v>157.3736999988832</v>
+        <v>156.8262999996273</v>
       </c>
     </row>
     <row r="7">
@@ -554,16 +554,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1049.951732201724</v>
+        <v>960.7187999999996</v>
       </c>
       <c r="C7" t="n">
-        <v>43.7479888417385</v>
+        <v>40.02994999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>45.22059279994502</v>
+        <v>44.0796</v>
       </c>
       <c r="E7" t="n">
-        <v>42.39162591352641</v>
+        <v>38.01290000000002</v>
       </c>
     </row>
     <row r="8">
@@ -573,16 +573,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13786.68072100424</v>
+        <v>13654.2472182226</v>
       </c>
       <c r="C8" t="n">
-        <v>574.4450300418436</v>
+        <v>568.9269674259417</v>
       </c>
       <c r="D8" t="n">
-        <v>581.4353528540194</v>
+        <v>575.6898924049455</v>
       </c>
       <c r="E8" t="n">
-        <v>569.454501910667</v>
+        <v>565.8167973675303</v>
       </c>
     </row>
   </sheetData>
